--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0123F397-50EF-4C8B-A4B3-AF796B72D53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2C50C1-8AD5-4C2D-A766-73D519ACE92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1050" windowWidth="14175" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2025" yWindow="0" windowWidth="12750" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="31">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -163,6 +163,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3295,14 +3311,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -3986,7 +4002,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4124,30 +4140,60 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
@@ -4157,6 +4203,12 @@
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
@@ -4166,23 +4218,47 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6">

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2C50C1-8AD5-4C2D-A766-73D519ACE92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7589C014-0B83-4EDE-95F3-A5BB3DAD9B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="0" windowWidth="12750" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="255" windowWidth="21600" windowHeight="14925" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="35">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -179,6 +179,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3311,14 +3327,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.45</v>
+        <v>0.77500000000000002</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -4002,7 +4018,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4266,24 +4282,48 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
@@ -4293,6 +4333,12 @@
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
@@ -4302,6 +4348,12 @@
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
@@ -4311,116 +4363,164 @@
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7589C014-0B83-4EDE-95F3-A5BB3DAD9B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BFC214-0017-4E33-A694-4A12E5614283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="255" windowWidth="21600" windowHeight="14925" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="0" windowWidth="21600" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
     <sheet name="listening" sheetId="1" r:id="rId2"/>
     <sheet name="reading" sheetId="2" r:id="rId3"/>
     <sheet name="review" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$C$102</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="44">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -195,6 +195,45 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>note</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>留意する</t>
+    <rPh sb="0" eb="2">
+      <t>リュウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3327,14 +3366,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.77500000000000002</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -3343,14 +3382,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4012,13 +4051,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4406,7 +4445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
@@ -4418,7 +4457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
@@ -4430,7 +4469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
@@ -4441,8 +4480,14 @@
       <c r="C35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="F35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
@@ -4454,76 +4499,148 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="B45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="B47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
+      </c>
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:1">

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BFC214-0017-4E33-A694-4A12E5614283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978236E3-006D-4CE1-BCCD-905E37BB1F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="0" windowWidth="21600" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="3825" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="46">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -234,6 +234,14 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3382,14 +3390,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4057,7 +4065,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4643,97 +4651,121 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978236E3-006D-4CE1-BCCD-905E37BB1F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB8D327-7CAF-4872-8966-84661CEBE668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="3825" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12855" yWindow="0" windowWidth="16635" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="49">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -242,6 +242,18 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4704,23 +4716,35 @@
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
+      <c r="B55" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
+      </c>
+      <c r="B56" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:3">

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB8D327-7CAF-4872-8966-84661CEBE668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD23ADC3-3EC1-4FFA-A3A8-D615A424976A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12855" yWindow="0" windowWidth="16635" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="2805" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="53">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -254,6 +254,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3402,14 +3418,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -3418,14 +3434,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -4077,7 +4093,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4719,6 +4735,9 @@
       <c r="B53" t="s">
         <v>46</v>
       </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
@@ -4728,6 +4747,9 @@
       <c r="B54" t="s">
         <v>47</v>
       </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
@@ -4737,6 +4759,9 @@
       <c r="B55" t="s">
         <v>48</v>
       </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
@@ -4746,41 +4771,80 @@
       <c r="B56" t="s">
         <v>46</v>
       </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
+      <c r="B57" t="s">
+        <v>49</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
+      <c r="B58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
+      <c r="B59" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
+      <c r="B60" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
+      <c r="B61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
+      </c>
+      <c r="B62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3">

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD23ADC3-3EC1-4FFA-A3A8-D615A424976A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D528C3-2383-446B-9C48-117A0DBE5CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="2805" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="645" yWindow="840" windowWidth="13830" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -254,6 +254,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3434,14 +3450,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.29166666666666669</v>
       </c>
     </row>
   </sheetData>
@@ -4093,7 +4109,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4852,104 +4868,146 @@
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
+      <c r="B63" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>54</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="B66" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="B68" t="s">
+        <v>56</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D528C3-2383-446B-9C48-117A0DBE5CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F305445-8B02-4663-A4BB-EA899DF1067A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="645" yWindow="840" windowWidth="13830" windowHeight="11295" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="480" windowWidth="11175" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="60">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -286,6 +286,18 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3450,14 +3462,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.29166666666666669</v>
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
@@ -4109,7 +4121,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4952,23 +4964,47 @@
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
+      <c r="B70" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
+      <c r="B71" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
+      <c r="B72" t="s">
+        <v>59</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
+      </c>
+      <c r="B73" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3">

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F305445-8B02-4663-A4BB-EA899DF1067A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9E07A2-7190-47AD-9FC1-CCC5850B8DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="480" windowWidth="11175" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15795" yWindow="0" windowWidth="13050" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="63">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -298,6 +298,18 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3462,14 +3474,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -4121,7 +4133,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5012,23 +5024,47 @@
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
+      <c r="B74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
+      <c r="B75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
+      <c r="B76" t="s">
+        <v>60</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
+      </c>
+      <c r="B77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3">

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9E07A2-7190-47AD-9FC1-CCC5850B8DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A45BEBD-647E-4122-9F2E-70AA9B7630AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15795" yWindow="0" windowWidth="13050" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="66">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -310,6 +310,18 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3474,14 +3486,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -4133,7 +4145,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5072,110 +5084,140 @@
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
+      <c r="B78" t="s">
+        <v>63</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
+      <c r="B79" t="s">
+        <v>63</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="B80" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" t="s">
+        <v>65</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A45BEBD-647E-4122-9F2E-70AA9B7630AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F32B42-C417-4679-9B2C-78CCF28BC300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="69">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -322,6 +322,18 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3486,14 +3498,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
     </row>
   </sheetData>
@@ -4145,7 +4157,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5144,29 +5156,59 @@
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
+      <c r="B83" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
+      <c r="B84" t="s">
+        <v>67</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
+      <c r="B85" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
+      <c r="B86" t="s">
+        <v>68</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
+      </c>
+      <c r="B87" t="s">
+        <v>66</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3">

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F32B42-C417-4679-9B2C-78CCF28BC300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFA48CB-9F43-4043-8982-78D1C98AE915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="75">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -330,6 +330,33 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>respondant</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回答者</t>
+    <rPh sb="0" eb="3">
+      <t>カイトウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3498,14 +3525,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.5625</v>
+        <v>0.64583333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -4157,7 +4184,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5127,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:7">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
@@ -5139,7 +5166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:7">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
@@ -5151,7 +5178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:7">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
@@ -5163,7 +5190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:7">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
@@ -5175,7 +5202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:7">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
@@ -5187,7 +5214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:7">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
@@ -5199,7 +5226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:7">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
@@ -5211,55 +5238,91 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:7">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="B88" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>70</v>
+      </c>
+      <c r="G88" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="B89" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="B90" t="s">
+        <v>73</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="B91" t="s">
+        <v>73</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="B92" t="s">
+        <v>74</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:7">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:7">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:7">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFA48CB-9F43-4043-8982-78D1C98AE915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B85BA7-A7D8-4FB5-BB0A-FD014E3B0402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="77">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -361,6 +361,14 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3525,14 +3533,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.64583333333333337</v>
+        <v>0.70833333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -4184,7 +4192,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5309,56 +5317,86 @@
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
+      <c r="B93" t="s">
+        <v>75</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
+      <c r="B94" t="s">
+        <v>75</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
+      <c r="B95" t="s">
+        <v>75</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>76</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>75</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B85BA7-A7D8-4FB5-BB0A-FD014E3B0402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95DE7C1-39C3-4366-BE40-92CE9D76E716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="80">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -369,6 +369,18 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3533,14 +3545,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.70833333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -4192,7 +4204,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5377,29 +5389,59 @@
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
+      <c r="B99" t="s">
+        <v>78</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
+      <c r="B100" t="s">
+        <v>78</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
+      <c r="B101" t="s">
+        <v>77</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
+      </c>
+      <c r="B102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95DE7C1-39C3-4366-BE40-92CE9D76E716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B19A2F-FB41-4DBE-9260-EFB3CFD32687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="80">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5458,7 +5458,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H314"/>
+  <dimension ref="A2:H329"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9126,6 +9126,111 @@
       </c>
       <c r="C314">
         <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315">
+        <v>101</v>
+      </c>
+      <c r="B315" t="s">
+        <v>8</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316">
+        <v>102</v>
+      </c>
+      <c r="B316" t="s">
+        <v>11</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317">
+        <v>103</v>
+      </c>
+      <c r="B317" t="s">
+        <v>11</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318">
+        <v>104</v>
+      </c>
+      <c r="B318" t="s">
+        <v>11</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319">
+        <v>105</v>
+      </c>
+      <c r="B319" t="s">
+        <v>10</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B19A2F-FB41-4DBE-9260-EFB3CFD32687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DCB1AD-425F-498B-B865-ABF6883BC426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="80">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5458,7 +5458,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H329"/>
+  <dimension ref="A2:H330"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9187,49 +9187,84 @@
       <c r="A320">
         <v>106</v>
       </c>
-    </row>
-    <row r="321" spans="1:1">
+      <c r="B320" t="s">
+        <v>8</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
       <c r="A321">
         <v>107</v>
       </c>
-    </row>
-    <row r="322" spans="1:1">
+      <c r="B321" t="s">
+        <v>10</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
       <c r="A322">
         <v>108</v>
       </c>
-    </row>
-    <row r="323" spans="1:1">
+      <c r="B322" t="s">
+        <v>8</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
       <c r="A323">
         <v>109</v>
       </c>
-    </row>
-    <row r="324" spans="1:1">
+      <c r="B323" t="s">
+        <v>8</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
       <c r="A324">
+        <v>110</v>
+      </c>
+      <c r="B324" t="s">
+        <v>9</v>
+      </c>
+      <c r="C324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325">
         <v>120</v>
       </c>
     </row>
-    <row r="325" spans="1:1">
-      <c r="A325">
+    <row r="326" spans="1:3">
+      <c r="A326">
         <v>121</v>
       </c>
     </row>
-    <row r="326" spans="1:1">
-      <c r="A326">
+    <row r="327" spans="1:3">
+      <c r="A327">
         <v>122</v>
       </c>
     </row>
-    <row r="327" spans="1:1">
-      <c r="A327">
+    <row r="328" spans="1:3">
+      <c r="A328">
         <v>123</v>
       </c>
     </row>
-    <row r="328" spans="1:1">
-      <c r="A328">
+    <row r="329" spans="1:3">
+      <c r="A329">
         <v>124</v>
       </c>
     </row>
-    <row r="329" spans="1:1">
-      <c r="A329">
+    <row r="330" spans="1:3">
+      <c r="A330">
         <v>125</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DCB1AD-425F-498B-B865-ABF6883BC426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECB5725-612B-4458-A051-1F66DA646ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="82">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -381,6 +381,20 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>completion</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了、完成</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンセイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5458,7 +5472,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H330"/>
+  <dimension ref="A2:H334"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9194,7 +9208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:7">
       <c r="A321">
         <v>107</v>
       </c>
@@ -9205,7 +9219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:7">
       <c r="A322">
         <v>108</v>
       </c>
@@ -9216,7 +9230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:7">
       <c r="A323">
         <v>109</v>
       </c>
@@ -9227,7 +9241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:7">
       <c r="A324">
         <v>110</v>
       </c>
@@ -9238,34 +9252,129 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:7">
       <c r="A325">
+        <v>111</v>
+      </c>
+      <c r="B325" t="s">
+        <v>9</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+      <c r="F325" t="s">
+        <v>80</v>
+      </c>
+      <c r="G325" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326">
+        <f>A325+1</f>
+        <v>112</v>
+      </c>
+      <c r="B326" t="s">
+        <v>8</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327">
+        <f t="shared" ref="A327:A336" si="12">A326+1</f>
+        <v>113</v>
+      </c>
+      <c r="B327" t="s">
+        <v>9</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328">
+        <f t="shared" si="12"/>
+        <v>114</v>
+      </c>
+      <c r="B328" t="s">
+        <v>11</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329">
+        <f t="shared" si="12"/>
+        <v>115</v>
+      </c>
+      <c r="B329" t="s">
+        <v>10</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330">
+        <f t="shared" si="12"/>
+        <v>116</v>
+      </c>
+      <c r="B330" t="s">
+        <v>10</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331">
+        <f t="shared" si="12"/>
+        <v>117</v>
+      </c>
+      <c r="B331" t="s">
+        <v>9</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332">
+        <f t="shared" si="12"/>
+        <v>118</v>
+      </c>
+      <c r="B332" t="s">
+        <v>10</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333">
+        <f t="shared" si="12"/>
+        <v>119</v>
+      </c>
+      <c r="B333" t="s">
+        <v>9</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334">
+        <f t="shared" si="12"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="326" spans="1:3">
-      <c r="A326">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3">
-      <c r="A327">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3">
-      <c r="A328">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3">
-      <c r="A329">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3">
-      <c r="A330">
-        <v>125</v>
+      <c r="B334" t="s">
+        <v>10</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECB5725-612B-4458-A051-1F66DA646ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B38D64-FADA-4109-9BDE-34B9B02BDEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="0" windowWidth="13050" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="0" windowWidth="15795" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="88">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -394,6 +394,39 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>likewise</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同様に</t>
+    <rPh sb="0" eb="2">
+      <t>ドウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>whether</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かどうか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>in case</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>した場合に備えて</t>
+    <rPh sb="2" eb="4">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ソナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5472,7 +5505,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H334"/>
+  <dimension ref="A2:I344"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9208,7 +9241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:9">
       <c r="A321">
         <v>107</v>
       </c>
@@ -9219,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:9">
       <c r="A322">
         <v>108</v>
       </c>
@@ -9230,7 +9263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:9">
       <c r="A323">
         <v>109</v>
       </c>
@@ -9241,7 +9274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:9">
       <c r="A324">
         <v>110</v>
       </c>
@@ -9252,7 +9285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:9">
       <c r="A325">
         <v>111</v>
       </c>
@@ -9269,7 +9302,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:9">
       <c r="A326">
         <f>A325+1</f>
         <v>112</v>
@@ -9281,9 +9314,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:9">
       <c r="A327">
-        <f t="shared" ref="A327:A336" si="12">A326+1</f>
+        <f t="shared" ref="A327:A347" si="12">A326+1</f>
         <v>113</v>
       </c>
       <c r="B327" t="s">
@@ -9293,7 +9326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:9">
       <c r="A328">
         <f t="shared" si="12"/>
         <v>114</v>
@@ -9305,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:9">
       <c r="A329">
         <f t="shared" si="12"/>
         <v>115</v>
@@ -9317,7 +9350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:9">
       <c r="A330">
         <f t="shared" si="12"/>
         <v>116</v>
@@ -9329,7 +9362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:9">
       <c r="A331">
         <f t="shared" si="12"/>
         <v>117</v>
@@ -9341,7 +9374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:9">
       <c r="A332">
         <f t="shared" si="12"/>
         <v>118</v>
@@ -9353,7 +9386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:9">
       <c r="A333">
         <f t="shared" si="12"/>
         <v>119</v>
@@ -9365,7 +9398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:9">
       <c r="A334">
         <f t="shared" si="12"/>
         <v>120</v>
@@ -9374,6 +9407,144 @@
         <v>10</v>
       </c>
       <c r="C334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9">
+      <c r="A335">
+        <f t="shared" si="12"/>
+        <v>121</v>
+      </c>
+      <c r="B335" t="s">
+        <v>8</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+      <c r="E335" t="s">
+        <v>82</v>
+      </c>
+      <c r="F335" t="s">
+        <v>83</v>
+      </c>
+      <c r="H335" t="s">
+        <v>86</v>
+      </c>
+      <c r="I335" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9">
+      <c r="A336">
+        <f t="shared" si="12"/>
+        <v>122</v>
+      </c>
+      <c r="B336" t="s">
+        <v>9</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="E336" t="s">
+        <v>84</v>
+      </c>
+      <c r="F336" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337">
+        <f t="shared" si="12"/>
+        <v>123</v>
+      </c>
+      <c r="B337" t="s">
+        <v>9</v>
+      </c>
+      <c r="C337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338">
+        <f t="shared" si="12"/>
+        <v>124</v>
+      </c>
+      <c r="B338" t="s">
+        <v>8</v>
+      </c>
+      <c r="C338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339">
+        <f t="shared" si="12"/>
+        <v>125</v>
+      </c>
+      <c r="B339" t="s">
+        <v>11</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340">
+        <f t="shared" si="12"/>
+        <v>126</v>
+      </c>
+      <c r="B340" t="s">
+        <v>8</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341">
+        <f t="shared" si="12"/>
+        <v>127</v>
+      </c>
+      <c r="B341" t="s">
+        <v>10</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342">
+        <f t="shared" si="12"/>
+        <v>128</v>
+      </c>
+      <c r="B342" t="s">
+        <v>8</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343">
+        <f t="shared" si="12"/>
+        <v>129</v>
+      </c>
+      <c r="B343" t="s">
+        <v>9</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344">
+        <f t="shared" si="12"/>
+        <v>130</v>
+      </c>
+      <c r="B344" t="s">
+        <v>9</v>
+      </c>
+      <c r="C344">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B38D64-FADA-4109-9BDE-34B9B02BDEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635F1642-5FFA-42FC-8F6E-B7D2F83C314B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="0" windowWidth="15795" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12750" yWindow="525" windowWidth="15795" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$C$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">reading!$A$2:$C$102</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="88">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5505,7 +5505,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I344"/>
+  <dimension ref="A2:I352"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9316,7 +9316,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327">
-        <f t="shared" ref="A327:A347" si="12">A326+1</f>
+        <f t="shared" ref="A327:A352" si="12">A326+1</f>
         <v>113</v>
       </c>
       <c r="B327" t="s">
@@ -9545,6 +9545,102 @@
         <v>9</v>
       </c>
       <c r="C344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345">
+        <f t="shared" si="12"/>
+        <v>131</v>
+      </c>
+      <c r="B345" t="s">
+        <v>11</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346">
+        <f t="shared" si="12"/>
+        <v>132</v>
+      </c>
+      <c r="B346" t="s">
+        <v>10</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347">
+        <f t="shared" si="12"/>
+        <v>133</v>
+      </c>
+      <c r="B347" t="s">
+        <v>11</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348">
+        <f t="shared" si="12"/>
+        <v>134</v>
+      </c>
+      <c r="B348" t="s">
+        <v>9</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349">
+        <f t="shared" si="12"/>
+        <v>135</v>
+      </c>
+      <c r="B349" t="s">
+        <v>8</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350">
+        <f t="shared" si="12"/>
+        <v>136</v>
+      </c>
+      <c r="B350" t="s">
+        <v>9</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351">
+        <f t="shared" si="12"/>
+        <v>137</v>
+      </c>
+      <c r="B351" t="s">
+        <v>10</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352">
+        <f t="shared" si="12"/>
+        <v>138</v>
+      </c>
+      <c r="B352" t="s">
+        <v>11</v>
+      </c>
+      <c r="C352">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635F1642-5FFA-42FC-8F6E-B7D2F83C314B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9488DB42-E02C-460C-AF73-C1359413D7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12750" yWindow="525" windowWidth="15795" windowHeight="14805" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$C$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">reading!$A$2:$C$102</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="88">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5505,10 +5505,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I352"/>
+  <dimension ref="A2:I375"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>101</v>
       </c>
@@ -5532,8 +5532,12 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="G3">
+        <f>_xlfn.NORM.S.INV(0.348)</f>
+        <v>-0.39072570019687003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <f>A3+1</f>
         <v>102</v>
@@ -5547,8 +5551,12 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="G4">
+        <f>G3*3</f>
+        <v>-1.1721771005906101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <f t="shared" ref="A5:A12" si="0">A4+1</f>
         <v>103</v>
@@ -5562,8 +5570,12 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="G5">
+        <f>20+G4</f>
+        <v>18.827822899409391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -5578,7 +5590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:7">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
@@ -5592,8 +5604,12 @@
       <c r="D7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="G7">
+        <f>_xlfn.NORM.S.INV(0.878)</f>
+        <v>1.1650469223056026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -5607,8 +5623,12 @@
       <c r="D8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="G8">
+        <f>G7*3</f>
+        <v>3.4951407669168075</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
@@ -5623,7 +5643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:7">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
@@ -5637,8 +5657,12 @@
       <c r="D10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="G10">
+        <f>_xlfn.NORM.S.INV(0.9)</f>
+        <v>1.2815515655446006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -5652,8 +5676,12 @@
       <c r="D11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="G11">
+        <f>G10*8.2</f>
+        <v>10.508722837465724</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -5667,8 +5695,12 @@
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="G12">
+        <f>G11+38.7</f>
+        <v>49.208722837465729</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>111</v>
       </c>
@@ -5679,7 +5711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>112</v>
       </c>
@@ -5690,7 +5722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>113</v>
       </c>
@@ -5701,7 +5733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>114</v>
       </c>
@@ -9316,7 +9348,7 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327">
-        <f t="shared" ref="A327:A352" si="12">A326+1</f>
+        <f t="shared" ref="A327:A360" si="12">A326+1</f>
         <v>113</v>
       </c>
       <c r="B327" t="s">
@@ -9642,6 +9674,244 @@
       </c>
       <c r="C352">
         <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353">
+        <f t="shared" si="12"/>
+        <v>139</v>
+      </c>
+      <c r="B353" t="s">
+        <v>8</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354">
+        <f t="shared" si="12"/>
+        <v>140</v>
+      </c>
+      <c r="B354" t="s">
+        <v>9</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355">
+        <f t="shared" si="12"/>
+        <v>141</v>
+      </c>
+      <c r="B355" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356">
+        <f t="shared" si="12"/>
+        <v>142</v>
+      </c>
+      <c r="B356" t="s">
+        <v>9</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357">
+        <f t="shared" si="12"/>
+        <v>143</v>
+      </c>
+      <c r="B357" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358">
+        <f t="shared" si="12"/>
+        <v>144</v>
+      </c>
+      <c r="B358" t="s">
+        <v>10</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359">
+        <f t="shared" si="12"/>
+        <v>145</v>
+      </c>
+      <c r="B359" t="s">
+        <v>8</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360">
+        <f t="shared" si="12"/>
+        <v>146</v>
+      </c>
+      <c r="B360" t="s">
+        <v>9</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361">
+        <v>147</v>
+      </c>
+      <c r="B361" t="s">
+        <v>9</v>
+      </c>
+      <c r="C361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362">
+        <v>148</v>
+      </c>
+      <c r="B362" t="s">
+        <v>8</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363">
+        <f t="shared" ref="A363:A375" si="13">A362+1</f>
+        <v>149</v>
+      </c>
+      <c r="B363" t="s">
+        <v>10</v>
+      </c>
+      <c r="C363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364">
+        <f t="shared" si="13"/>
+        <v>150</v>
+      </c>
+      <c r="B364" t="s">
+        <v>9</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365">
+        <f t="shared" si="13"/>
+        <v>151</v>
+      </c>
+      <c r="B365" t="s">
+        <v>8</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366">
+        <f t="shared" si="13"/>
+        <v>152</v>
+      </c>
+      <c r="B366" t="s">
+        <v>11</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367">
+        <f t="shared" si="13"/>
+        <v>153</v>
+      </c>
+      <c r="B367" t="s">
+        <v>8</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368">
+        <f t="shared" si="13"/>
+        <v>154</v>
+      </c>
+      <c r="B368" t="s">
+        <v>10</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <f t="shared" si="13"/>
+        <v>155</v>
+      </c>
+      <c r="B369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <f t="shared" si="13"/>
+        <v>156</v>
+      </c>
+      <c r="B370" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <f t="shared" si="13"/>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <f t="shared" si="13"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <f t="shared" si="13"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <f t="shared" si="13"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <f t="shared" si="13"/>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9488DB42-E02C-460C-AF73-C1359413D7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16DA3BC-9C1F-4B44-B213-49E495000681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="88">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -9866,7 +9866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" spans="1:3">
       <c r="A369">
         <f t="shared" si="13"/>
         <v>155</v>
@@ -9874,8 +9874,11 @@
       <c r="B369" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="370" spans="1:2">
+      <c r="C369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
       <c r="A370">
         <f t="shared" si="13"/>
         <v>156</v>
@@ -9883,32 +9886,59 @@
       <c r="B370" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="371" spans="1:2">
+      <c r="C370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
       <c r="A371">
         <f t="shared" si="13"/>
         <v>157</v>
       </c>
-    </row>
-    <row r="372" spans="1:2">
+      <c r="B371" t="s">
+        <v>10</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
       <c r="A372">
         <f t="shared" si="13"/>
         <v>158</v>
       </c>
-    </row>
-    <row r="373" spans="1:2">
+      <c r="B372" t="s">
+        <v>11</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
       <c r="A373">
         <f t="shared" si="13"/>
         <v>159</v>
       </c>
-    </row>
-    <row r="374" spans="1:2">
+      <c r="B373" t="s">
+        <v>8</v>
+      </c>
+      <c r="C373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
       <c r="A374">
         <f t="shared" si="13"/>
         <v>160</v>
       </c>
-    </row>
-    <row r="375" spans="1:2">
+      <c r="B374" t="s">
+        <v>11</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
       <c r="A375">
         <f t="shared" si="13"/>
         <v>161</v>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16DA3BC-9C1F-4B44-B213-49E495000681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC18D054-933D-44E9-B037-2D8F7A3DEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="88">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5505,7 +5505,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I375"/>
+  <dimension ref="A2:I381"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -9796,7 +9796,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <f t="shared" ref="A363:A375" si="13">A362+1</f>
+        <f t="shared" ref="A363:A381" si="13">A362+1</f>
         <v>149</v>
       </c>
       <c r="B363" t="s">
@@ -9942,6 +9942,84 @@
       <c r="A375">
         <f t="shared" si="13"/>
         <v>161</v>
+      </c>
+      <c r="B375" t="s">
+        <v>8</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376">
+        <f t="shared" si="13"/>
+        <v>162</v>
+      </c>
+      <c r="B376" t="s">
+        <v>8</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377">
+        <f t="shared" si="13"/>
+        <v>163</v>
+      </c>
+      <c r="B377" t="s">
+        <v>10</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378">
+        <f t="shared" si="13"/>
+        <v>164</v>
+      </c>
+      <c r="B378" t="s">
+        <v>8</v>
+      </c>
+      <c r="C378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379">
+        <f t="shared" si="13"/>
+        <v>165</v>
+      </c>
+      <c r="B379" t="s">
+        <v>9</v>
+      </c>
+      <c r="C379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380">
+        <f t="shared" si="13"/>
+        <v>166</v>
+      </c>
+      <c r="B380" t="s">
+        <v>10</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381">
+        <f t="shared" si="13"/>
+        <v>167</v>
+      </c>
+      <c r="B381" t="s">
+        <v>9</v>
+      </c>
+      <c r="C381">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC18D054-933D-44E9-B037-2D8F7A3DEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE09D157-E216-48A1-8393-6999F5011BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="0" windowWidth="15330" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="88">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5505,7 +5505,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I381"/>
+  <dimension ref="A2:I389"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -9796,7 +9796,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <f t="shared" ref="A363:A381" si="13">A362+1</f>
+        <f t="shared" ref="A363:A389" si="13">A362+1</f>
         <v>149</v>
       </c>
       <c r="B363" t="s">
@@ -10020,6 +10020,66 @@
       </c>
       <c r="C381">
         <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382">
+        <f t="shared" si="13"/>
+        <v>168</v>
+      </c>
+      <c r="B382" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383">
+        <f t="shared" si="13"/>
+        <v>169</v>
+      </c>
+      <c r="B383" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384">
+        <f t="shared" si="13"/>
+        <v>170</v>
+      </c>
+      <c r="B384" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <f t="shared" si="13"/>
+        <v>171</v>
+      </c>
+      <c r="B385" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <f t="shared" si="13"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <f t="shared" si="13"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <f t="shared" si="13"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <f t="shared" si="13"/>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE09D157-E216-48A1-8393-6999F5011BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51174F2-1378-425E-AFCA-1B2563A30EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="0" windowWidth="15330" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="0" windowWidth="16695" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="88">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -10030,6 +10030,9 @@
       <c r="B382" t="s">
         <v>10</v>
       </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383">
@@ -10039,6 +10042,9 @@
       <c r="B383" t="s">
         <v>8</v>
       </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384">
@@ -10048,8 +10054,11 @@
       <c r="B384" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="385" spans="1:2">
+      <c r="C384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
       <c r="A385">
         <f t="shared" si="13"/>
         <v>171</v>
@@ -10057,29 +10066,56 @@
       <c r="B385" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="386" spans="1:2">
+      <c r="C385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
       <c r="A386">
         <f t="shared" si="13"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="387" spans="1:2">
+      <c r="B386" t="s">
+        <v>8</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
       <c r="A387">
         <f t="shared" si="13"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="388" spans="1:2">
+      <c r="B387" t="s">
+        <v>11</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
       <c r="A388">
         <f t="shared" si="13"/>
         <v>174</v>
       </c>
-    </row>
-    <row r="389" spans="1:2">
+      <c r="B388" t="s">
+        <v>8</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
       <c r="A389">
         <f t="shared" si="13"/>
         <v>175</v>
+      </c>
+      <c r="B389" t="s">
+        <v>10</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51174F2-1378-425E-AFCA-1B2563A30EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31906DEF-7224-4644-8A05-A8A18EC52013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="0" windowWidth="16695" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5490" yWindow="1515" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="90">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -427,6 +427,17 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>ソナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>abandon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>放棄する</t>
+    <rPh sb="0" eb="2">
+      <t>ホウキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5505,7 +5516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I389"/>
+  <dimension ref="A2:I414"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -9796,7 +9807,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <f t="shared" ref="A363:A389" si="13">A362+1</f>
+        <f t="shared" ref="A363:A414" si="13">A362+1</f>
         <v>149</v>
       </c>
       <c r="B363" t="s">
@@ -10116,6 +10127,312 @@
       </c>
       <c r="C389">
         <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390">
+        <f t="shared" si="13"/>
+        <v>176</v>
+      </c>
+      <c r="B390" t="s">
+        <v>8</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391">
+        <f t="shared" si="13"/>
+        <v>177</v>
+      </c>
+      <c r="B391" t="s">
+        <v>9</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392">
+        <f t="shared" si="13"/>
+        <v>178</v>
+      </c>
+      <c r="B392" t="s">
+        <v>11</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393">
+        <f t="shared" si="13"/>
+        <v>179</v>
+      </c>
+      <c r="B393" t="s">
+        <v>10</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394">
+        <f t="shared" si="13"/>
+        <v>180</v>
+      </c>
+      <c r="B394" t="s">
+        <v>10</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395">
+        <f t="shared" si="13"/>
+        <v>181</v>
+      </c>
+      <c r="B395" t="s">
+        <v>9</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396">
+        <f t="shared" si="13"/>
+        <v>182</v>
+      </c>
+      <c r="B396" t="s">
+        <v>11</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397">
+        <f t="shared" si="13"/>
+        <v>183</v>
+      </c>
+      <c r="B397" t="s">
+        <v>8</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398">
+        <f t="shared" si="13"/>
+        <v>184</v>
+      </c>
+      <c r="B398" t="s">
+        <v>8</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399">
+        <f t="shared" si="13"/>
+        <v>185</v>
+      </c>
+      <c r="B399" t="s">
+        <v>9</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400">
+        <f t="shared" si="13"/>
+        <v>186</v>
+      </c>
+      <c r="B400" t="s">
+        <v>8</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401">
+        <f t="shared" si="13"/>
+        <v>187</v>
+      </c>
+      <c r="B401" t="s">
+        <v>11</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402">
+        <f t="shared" si="13"/>
+        <v>188</v>
+      </c>
+      <c r="B402" t="s">
+        <v>8</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
+      <c r="A403">
+        <f t="shared" si="13"/>
+        <v>189</v>
+      </c>
+      <c r="B403" t="s">
+        <v>8</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
+      <c r="A404">
+        <f t="shared" si="13"/>
+        <v>190</v>
+      </c>
+      <c r="B404" t="s">
+        <v>10</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7">
+      <c r="A405">
+        <f t="shared" si="13"/>
+        <v>191</v>
+      </c>
+      <c r="B405" t="s">
+        <v>10</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406">
+        <f t="shared" si="13"/>
+        <v>192</v>
+      </c>
+      <c r="B406" t="s">
+        <v>10</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
+      <c r="A407">
+        <f t="shared" si="13"/>
+        <v>193</v>
+      </c>
+      <c r="B407" t="s">
+        <v>10</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
+      <c r="A408">
+        <f t="shared" si="13"/>
+        <v>194</v>
+      </c>
+      <c r="B408" t="s">
+        <v>8</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
+      <c r="A409">
+        <f t="shared" si="13"/>
+        <v>195</v>
+      </c>
+      <c r="B409" t="s">
+        <v>11</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7">
+      <c r="A410">
+        <f t="shared" si="13"/>
+        <v>196</v>
+      </c>
+      <c r="B410" t="s">
+        <v>9</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7">
+      <c r="A411">
+        <f t="shared" si="13"/>
+        <v>197</v>
+      </c>
+      <c r="B411" t="s">
+        <v>8</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="F411" t="s">
+        <v>88</v>
+      </c>
+      <c r="G411" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7">
+      <c r="A412">
+        <f t="shared" si="13"/>
+        <v>198</v>
+      </c>
+      <c r="B412" t="s">
+        <v>8</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7">
+      <c r="A413">
+        <f t="shared" si="13"/>
+        <v>199</v>
+      </c>
+      <c r="B413" t="s">
+        <v>9</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7">
+      <c r="A414">
+        <f t="shared" si="13"/>
+        <v>200</v>
+      </c>
+      <c r="B414" t="s">
+        <v>8</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31906DEF-7224-4644-8A05-A8A18EC52013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF3BC41-9490-4DA7-A6B5-EAAE1FD98A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5490" yWindow="1515" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1650" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="90">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5516,7 +5516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I414"/>
+  <dimension ref="A2:I430"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -9807,7 +9807,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <f t="shared" ref="A363:A414" si="13">A362+1</f>
+        <f t="shared" ref="A363:A426" si="13">A362+1</f>
         <v>149</v>
       </c>
       <c r="B363" t="s">
@@ -10433,6 +10433,161 @@
       </c>
       <c r="C414">
         <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7">
+      <c r="A415">
+        <v>101</v>
+      </c>
+      <c r="B415" t="s">
+        <v>8</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7">
+      <c r="A416">
+        <f t="shared" si="13"/>
+        <v>102</v>
+      </c>
+      <c r="B416" t="s">
+        <v>11</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417">
+        <f t="shared" si="13"/>
+        <v>103</v>
+      </c>
+      <c r="B417" t="s">
+        <v>11</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418">
+        <f t="shared" si="13"/>
+        <v>104</v>
+      </c>
+      <c r="B418" t="s">
+        <v>11</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419">
+        <f t="shared" si="13"/>
+        <v>105</v>
+      </c>
+      <c r="B419" t="s">
+        <v>10</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420">
+        <f t="shared" si="13"/>
+        <v>106</v>
+      </c>
+      <c r="B420" t="s">
+        <v>8</v>
+      </c>
+      <c r="C420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421">
+        <f t="shared" si="13"/>
+        <v>107</v>
+      </c>
+      <c r="B421" t="s">
+        <v>11</v>
+      </c>
+      <c r="C421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422">
+        <f t="shared" si="13"/>
+        <v>108</v>
+      </c>
+      <c r="B422" t="s">
+        <v>8</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423">
+        <f t="shared" si="13"/>
+        <v>109</v>
+      </c>
+      <c r="B423" t="s">
+        <v>8</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424">
+        <f t="shared" si="13"/>
+        <v>110</v>
+      </c>
+      <c r="B424" t="s">
+        <v>9</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425">
+        <f t="shared" si="13"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426">
+        <f t="shared" si="13"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427">
+        <f t="shared" ref="A427:A430" si="14">A426+1</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428">
+        <f t="shared" si="14"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429">
+        <f t="shared" si="14"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430">
+        <f t="shared" si="14"/>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF3BC41-9490-4DA7-A6B5-EAAE1FD98A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84AC795-CD74-46AC-B30A-601E6885F30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1650" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="0" windowWidth="14535" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="90">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5516,7 +5516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I430"/>
+  <dimension ref="A2:I434"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -10559,17 +10559,35 @@
         <f t="shared" si="13"/>
         <v>111</v>
       </c>
+      <c r="B425" t="s">
+        <v>9</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426">
         <f t="shared" si="13"/>
         <v>112</v>
       </c>
+      <c r="B426" t="s">
+        <v>8</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
     </row>
     <row r="427" spans="1:3">
       <c r="A427">
-        <f t="shared" ref="A427:A430" si="14">A426+1</f>
+        <f t="shared" ref="A427:A434" si="14">A426+1</f>
         <v>113</v>
+      </c>
+      <c r="B427" t="s">
+        <v>9</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -10577,17 +10595,83 @@
         <f t="shared" si="14"/>
         <v>114</v>
       </c>
+      <c r="B428" t="s">
+        <v>11</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429">
         <f t="shared" si="14"/>
         <v>115</v>
       </c>
+      <c r="B429" t="s">
+        <v>10</v>
+      </c>
+      <c r="C429">
+        <v>1</v>
+      </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430">
         <f t="shared" si="14"/>
         <v>116</v>
+      </c>
+      <c r="B430" t="s">
+        <v>10</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431">
+        <f t="shared" si="14"/>
+        <v>117</v>
+      </c>
+      <c r="B431" t="s">
+        <v>9</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3">
+      <c r="A432">
+        <f t="shared" si="14"/>
+        <v>118</v>
+      </c>
+      <c r="B432" t="s">
+        <v>10</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3">
+      <c r="A433">
+        <f t="shared" si="14"/>
+        <v>119</v>
+      </c>
+      <c r="B433" t="s">
+        <v>9</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434">
+        <f t="shared" si="14"/>
+        <v>120</v>
+      </c>
+      <c r="B434" t="s">
+        <v>10</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84AC795-CD74-46AC-B30A-601E6885F30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B220BD-946E-454F-9430-9A7676C81D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="0" windowWidth="14535" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="570" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="90">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5516,7 +5516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I434"/>
+  <dimension ref="A2:I444"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -10580,7 +10580,7 @@
     </row>
     <row r="427" spans="1:3">
       <c r="A427">
-        <f t="shared" ref="A427:A434" si="14">A426+1</f>
+        <f t="shared" ref="A427:A444" si="14">A426+1</f>
         <v>113</v>
       </c>
       <c r="B427" t="s">
@@ -10671,6 +10671,126 @@
         <v>10</v>
       </c>
       <c r="C434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435">
+        <f t="shared" si="14"/>
+        <v>121</v>
+      </c>
+      <c r="B435" t="s">
+        <v>8</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436">
+        <f t="shared" si="14"/>
+        <v>122</v>
+      </c>
+      <c r="B436" t="s">
+        <v>9</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437">
+        <f t="shared" si="14"/>
+        <v>123</v>
+      </c>
+      <c r="B437" t="s">
+        <v>9</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438">
+        <f t="shared" si="14"/>
+        <v>124</v>
+      </c>
+      <c r="B438" t="s">
+        <v>8</v>
+      </c>
+      <c r="C438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439">
+        <f t="shared" si="14"/>
+        <v>125</v>
+      </c>
+      <c r="B439" t="s">
+        <v>10</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440">
+        <f t="shared" si="14"/>
+        <v>126</v>
+      </c>
+      <c r="B440" t="s">
+        <v>10</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441">
+        <f t="shared" si="14"/>
+        <v>127</v>
+      </c>
+      <c r="B441" t="s">
+        <v>10</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442">
+        <f t="shared" si="14"/>
+        <v>128</v>
+      </c>
+      <c r="B442" t="s">
+        <v>8</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443">
+        <f t="shared" si="14"/>
+        <v>129</v>
+      </c>
+      <c r="B443" t="s">
+        <v>9</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444">
+        <f t="shared" si="14"/>
+        <v>130</v>
+      </c>
+      <c r="B444" t="s">
+        <v>9</v>
+      </c>
+      <c r="C444">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B220BD-946E-454F-9430-9A7676C81D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DF9544-595A-429B-99F4-07107F7187C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="570" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="435" yWindow="0" windowWidth="15330" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="90">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5516,7 +5516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I444"/>
+  <dimension ref="A2:I454"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -10791,6 +10791,116 @@
         <v>9</v>
       </c>
       <c r="C444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445">
+        <v>121</v>
+      </c>
+      <c r="B445" t="s">
+        <v>8</v>
+      </c>
+      <c r="C445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446">
+        <v>122</v>
+      </c>
+      <c r="B446" t="s">
+        <v>8</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447">
+        <v>123</v>
+      </c>
+      <c r="B447" t="s">
+        <v>9</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448">
+        <v>124</v>
+      </c>
+      <c r="B448" t="s">
+        <v>9</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449">
+        <v>125</v>
+      </c>
+      <c r="B449" t="s">
+        <v>11</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450">
+        <v>126</v>
+      </c>
+      <c r="B450" t="s">
+        <v>9</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451">
+        <v>127</v>
+      </c>
+      <c r="B451" t="s">
+        <v>8</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452">
+        <v>128</v>
+      </c>
+      <c r="B452" t="s">
+        <v>10</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453">
+        <v>129</v>
+      </c>
+      <c r="B453" t="s">
+        <v>8</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3">
+      <c r="A454">
+        <v>130</v>
+      </c>
+      <c r="B454" t="s">
+        <v>9</v>
+      </c>
+      <c r="C454">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DF9544-595A-429B-99F4-07107F7187C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71FAA97-385F-4B01-A7F3-FF880D27221D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="435" yWindow="0" windowWidth="15330" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13590" yWindow="0" windowWidth="16155" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="95">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -438,6 +438,29 @@
     <t>放棄する</t>
     <rPh sb="0" eb="2">
       <t>ホウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>assessed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>assesed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>urge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>comprehensive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総合リスト</t>
+    <rPh sb="0" eb="2">
+      <t>ソウゴウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5516,7 +5539,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I454"/>
+  <dimension ref="A2:I480"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -10838,7 +10861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:6">
       <c r="A449">
         <v>125</v>
       </c>
@@ -10849,7 +10872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:3">
+    <row r="450" spans="1:6">
       <c r="A450">
         <v>126</v>
       </c>
@@ -10860,7 +10883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:6">
       <c r="A451">
         <v>127</v>
       </c>
@@ -10871,7 +10894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:6">
       <c r="A452">
         <v>128</v>
       </c>
@@ -10882,7 +10905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:6">
       <c r="A453">
         <v>129</v>
       </c>
@@ -10893,7 +10916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:3">
+    <row r="454" spans="1:6">
       <c r="A454">
         <v>130</v>
       </c>
@@ -10901,6 +10924,325 @@
         <v>9</v>
       </c>
       <c r="C454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
+      <c r="A455">
+        <v>121</v>
+      </c>
+      <c r="B455" t="s">
+        <v>8</v>
+      </c>
+      <c r="C455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
+      <c r="A456">
+        <v>122</v>
+      </c>
+      <c r="B456" t="s">
+        <v>8</v>
+      </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6">
+      <c r="A457">
+        <v>123</v>
+      </c>
+      <c r="B457" t="s">
+        <v>9</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
+      <c r="A458">
+        <v>124</v>
+      </c>
+      <c r="B458" t="s">
+        <v>9</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
+      <c r="A459">
+        <v>125</v>
+      </c>
+      <c r="B459" t="s">
+        <v>11</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6">
+      <c r="A460">
+        <v>126</v>
+      </c>
+      <c r="B460" t="s">
+        <v>9</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6">
+      <c r="A461">
+        <v>127</v>
+      </c>
+      <c r="B461" t="s">
+        <v>10</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
+      <c r="A462">
+        <v>128</v>
+      </c>
+      <c r="B462" t="s">
+        <v>8</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
+      <c r="A463">
+        <v>129</v>
+      </c>
+      <c r="B463" t="s">
+        <v>10</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463" t="s">
+        <v>90</v>
+      </c>
+      <c r="E463" t="s">
+        <v>91</v>
+      </c>
+      <c r="F463" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6">
+      <c r="A464">
+        <v>130</v>
+      </c>
+      <c r="B464" t="s">
+        <v>9</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6">
+      <c r="A465">
+        <v>131</v>
+      </c>
+      <c r="B465" t="s">
+        <v>11</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
+      <c r="A466">
+        <f t="shared" ref="A466:A480" si="15">A465+1</f>
+        <v>132</v>
+      </c>
+      <c r="B466" t="s">
+        <v>8</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+      <c r="D466" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6">
+      <c r="A467">
+        <f t="shared" si="15"/>
+        <v>133</v>
+      </c>
+      <c r="B467" t="s">
+        <v>11</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6">
+      <c r="A468">
+        <f t="shared" si="15"/>
+        <v>134</v>
+      </c>
+      <c r="B468" t="s">
+        <v>9</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+      <c r="E468" t="s">
+        <v>93</v>
+      </c>
+      <c r="F468" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
+      <c r="A469">
+        <f t="shared" si="15"/>
+        <v>135</v>
+      </c>
+      <c r="B469" t="s">
+        <v>11</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
+      <c r="A470">
+        <f t="shared" si="15"/>
+        <v>136</v>
+      </c>
+      <c r="B470" t="s">
+        <v>8</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
+      <c r="A471">
+        <f t="shared" si="15"/>
+        <v>137</v>
+      </c>
+      <c r="B471" t="s">
+        <v>10</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6">
+      <c r="A472">
+        <f t="shared" si="15"/>
+        <v>138</v>
+      </c>
+      <c r="B472" t="s">
+        <v>11</v>
+      </c>
+      <c r="C472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
+      <c r="A473">
+        <f t="shared" si="15"/>
+        <v>139</v>
+      </c>
+      <c r="B473" t="s">
+        <v>8</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
+      <c r="A474">
+        <f t="shared" si="15"/>
+        <v>140</v>
+      </c>
+      <c r="B474" t="s">
+        <v>9</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6">
+      <c r="A475">
+        <f t="shared" si="15"/>
+        <v>141</v>
+      </c>
+      <c r="B475" t="s">
+        <v>9</v>
+      </c>
+      <c r="C475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
+      <c r="A476">
+        <f t="shared" si="15"/>
+        <v>142</v>
+      </c>
+      <c r="B476" t="s">
+        <v>10</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
+      <c r="A477">
+        <f t="shared" si="15"/>
+        <v>143</v>
+      </c>
+      <c r="B477" t="s">
+        <v>10</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6">
+      <c r="A478">
+        <f t="shared" si="15"/>
+        <v>144</v>
+      </c>
+      <c r="B478" t="s">
+        <v>10</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
+      <c r="A479">
+        <f t="shared" si="15"/>
+        <v>145</v>
+      </c>
+      <c r="B479" t="s">
+        <v>11</v>
+      </c>
+      <c r="C479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
+      <c r="A480">
+        <f t="shared" si="15"/>
+        <v>146</v>
+      </c>
+      <c r="B480" t="s">
+        <v>8</v>
+      </c>
+      <c r="C480">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71FAA97-385F-4B01-A7F3-FF880D27221D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4A1253-F2AA-42F9-AF09-7F4EF0CF3AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13590" yWindow="0" windowWidth="16155" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13965" yWindow="0" windowWidth="14400" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="95">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5539,7 +5539,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I480"/>
+  <dimension ref="A2:I490"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11059,7 +11059,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466">
-        <f t="shared" ref="A466:A480" si="15">A465+1</f>
+        <f t="shared" ref="A466:A490" si="15">A465+1</f>
         <v>132</v>
       </c>
       <c r="B466" t="s">
@@ -11243,6 +11243,125 @@
         <v>8</v>
       </c>
       <c r="C480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3">
+      <c r="A481">
+        <v>111</v>
+      </c>
+      <c r="B481" t="s">
+        <v>9</v>
+      </c>
+      <c r="C481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3">
+      <c r="A482">
+        <f t="shared" si="15"/>
+        <v>112</v>
+      </c>
+      <c r="B482" t="s">
+        <v>8</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3">
+      <c r="A483">
+        <f t="shared" si="15"/>
+        <v>113</v>
+      </c>
+      <c r="B483" t="s">
+        <v>8</v>
+      </c>
+      <c r="C483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484">
+        <f t="shared" si="15"/>
+        <v>114</v>
+      </c>
+      <c r="B484" t="s">
+        <v>11</v>
+      </c>
+      <c r="C484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485">
+        <f t="shared" si="15"/>
+        <v>115</v>
+      </c>
+      <c r="B485" t="s">
+        <v>10</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486">
+        <f t="shared" si="15"/>
+        <v>116</v>
+      </c>
+      <c r="B486" t="s">
+        <v>10</v>
+      </c>
+      <c r="C486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487">
+        <f t="shared" si="15"/>
+        <v>117</v>
+      </c>
+      <c r="B487" t="s">
+        <v>9</v>
+      </c>
+      <c r="C487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488">
+        <f t="shared" si="15"/>
+        <v>118</v>
+      </c>
+      <c r="B488" t="s">
+        <v>10</v>
+      </c>
+      <c r="C488">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489">
+        <f t="shared" si="15"/>
+        <v>119</v>
+      </c>
+      <c r="B489" t="s">
+        <v>8</v>
+      </c>
+      <c r="C489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="B490" t="s">
+        <v>10</v>
+      </c>
+      <c r="C490">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4A1253-F2AA-42F9-AF09-7F4EF0CF3AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8BDEF9-F866-4E3F-A6AB-C2FA5E183F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13965" yWindow="0" windowWidth="14400" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="97">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -461,6 +461,17 @@
     <t>総合リスト</t>
     <rPh sb="0" eb="2">
       <t>ソウゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>over</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>～の間に</t>
+    <rPh sb="2" eb="3">
+      <t>アイダ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5539,7 +5550,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I490"/>
+  <dimension ref="A2:I521"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11059,7 +11070,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466">
-        <f t="shared" ref="A466:A490" si="15">A465+1</f>
+        <f t="shared" ref="A466:A521" si="15">A465+1</f>
         <v>132</v>
       </c>
       <c r="B466" t="s">
@@ -11362,6 +11373,381 @@
         <v>10</v>
       </c>
       <c r="C490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3">
+      <c r="A491">
+        <f t="shared" si="15"/>
+        <v>121</v>
+      </c>
+      <c r="B491" t="s">
+        <v>8</v>
+      </c>
+      <c r="C491">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492">
+        <f t="shared" si="15"/>
+        <v>122</v>
+      </c>
+      <c r="B492" t="s">
+        <v>8</v>
+      </c>
+      <c r="C492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493">
+        <f t="shared" si="15"/>
+        <v>123</v>
+      </c>
+      <c r="B493" t="s">
+        <v>9</v>
+      </c>
+      <c r="C493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494">
+        <f t="shared" si="15"/>
+        <v>124</v>
+      </c>
+      <c r="B494" t="s">
+        <v>9</v>
+      </c>
+      <c r="C494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3">
+      <c r="A495">
+        <f t="shared" si="15"/>
+        <v>125</v>
+      </c>
+      <c r="B495" t="s">
+        <v>11</v>
+      </c>
+      <c r="C495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3">
+      <c r="A496">
+        <f t="shared" si="15"/>
+        <v>126</v>
+      </c>
+      <c r="B496" t="s">
+        <v>10</v>
+      </c>
+      <c r="C496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6">
+      <c r="A497">
+        <f t="shared" si="15"/>
+        <v>127</v>
+      </c>
+      <c r="B497" t="s">
+        <v>8</v>
+      </c>
+      <c r="C497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6">
+      <c r="A498">
+        <f t="shared" si="15"/>
+        <v>128</v>
+      </c>
+      <c r="B498" t="s">
+        <v>8</v>
+      </c>
+      <c r="C498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6">
+      <c r="A499">
+        <f t="shared" si="15"/>
+        <v>129</v>
+      </c>
+      <c r="B499" t="s">
+        <v>8</v>
+      </c>
+      <c r="C499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6">
+      <c r="A500">
+        <f t="shared" si="15"/>
+        <v>130</v>
+      </c>
+      <c r="B500" t="s">
+        <v>10</v>
+      </c>
+      <c r="C500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6">
+      <c r="A501">
+        <v>126</v>
+      </c>
+      <c r="B501" t="s">
+        <v>9</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6">
+      <c r="A502">
+        <f t="shared" si="15"/>
+        <v>127</v>
+      </c>
+      <c r="B502" t="s">
+        <v>10</v>
+      </c>
+      <c r="C502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6">
+      <c r="A503">
+        <f t="shared" si="15"/>
+        <v>128</v>
+      </c>
+      <c r="B503" t="s">
+        <v>11</v>
+      </c>
+      <c r="C503">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
+      <c r="A504">
+        <f t="shared" si="15"/>
+        <v>129</v>
+      </c>
+      <c r="B504" t="s">
+        <v>9</v>
+      </c>
+      <c r="C504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6">
+      <c r="A505">
+        <f t="shared" si="15"/>
+        <v>130</v>
+      </c>
+      <c r="B505" t="s">
+        <v>9</v>
+      </c>
+      <c r="C505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
+      <c r="A506">
+        <v>131</v>
+      </c>
+      <c r="B506" t="s">
+        <v>11</v>
+      </c>
+      <c r="C506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
+      <c r="A507">
+        <f t="shared" si="15"/>
+        <v>132</v>
+      </c>
+      <c r="B507" t="s">
+        <v>8</v>
+      </c>
+      <c r="C507">
+        <v>1</v>
+      </c>
+      <c r="E507" t="s">
+        <v>95</v>
+      </c>
+      <c r="F507" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
+      <c r="A508">
+        <f t="shared" si="15"/>
+        <v>133</v>
+      </c>
+      <c r="B508" t="s">
+        <v>10</v>
+      </c>
+      <c r="C508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
+      <c r="A509">
+        <f t="shared" si="15"/>
+        <v>134</v>
+      </c>
+      <c r="B509" t="s">
+        <v>9</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
+      <c r="A510">
+        <v>135</v>
+      </c>
+      <c r="B510" t="s">
+        <v>9</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6">
+      <c r="A511">
+        <f t="shared" si="15"/>
+        <v>136</v>
+      </c>
+      <c r="B511" t="s">
+        <v>8</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6">
+      <c r="A512">
+        <f t="shared" si="15"/>
+        <v>137</v>
+      </c>
+      <c r="B512" t="s">
+        <v>10</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3">
+      <c r="A513">
+        <f t="shared" si="15"/>
+        <v>138</v>
+      </c>
+      <c r="B513" t="s">
+        <v>11</v>
+      </c>
+      <c r="C513">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3">
+      <c r="A514">
+        <f t="shared" si="15"/>
+        <v>139</v>
+      </c>
+      <c r="B514" t="s">
+        <v>8</v>
+      </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3">
+      <c r="A515">
+        <f t="shared" si="15"/>
+        <v>140</v>
+      </c>
+      <c r="B515" t="s">
+        <v>9</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3">
+      <c r="A516">
+        <f t="shared" si="15"/>
+        <v>141</v>
+      </c>
+      <c r="B516" t="s">
+        <v>9</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3">
+      <c r="A517">
+        <f t="shared" si="15"/>
+        <v>142</v>
+      </c>
+      <c r="B517" t="s">
+        <v>10</v>
+      </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3">
+      <c r="A518">
+        <f t="shared" si="15"/>
+        <v>143</v>
+      </c>
+      <c r="B518" t="s">
+        <v>10</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3">
+      <c r="A519">
+        <f t="shared" si="15"/>
+        <v>144</v>
+      </c>
+      <c r="B519" t="s">
+        <v>10</v>
+      </c>
+      <c r="C519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3">
+      <c r="A520">
+        <f t="shared" si="15"/>
+        <v>145</v>
+      </c>
+      <c r="B520" t="s">
+        <v>11</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3">
+      <c r="A521">
+        <f t="shared" si="15"/>
+        <v>146</v>
+      </c>
+      <c r="B521" t="s">
+        <v>8</v>
+      </c>
+      <c r="C521">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8BDEF9-F866-4E3F-A6AB-C2FA5E183F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B871E3-53D0-46CF-BCA2-CC931A6184D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="98">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -474,6 +474,9 @@
       <t>アイダ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -5550,7 +5553,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I521"/>
+  <dimension ref="A2:I530"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11070,7 +11073,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466">
-        <f t="shared" ref="A466:A521" si="15">A465+1</f>
+        <f t="shared" ref="A466:A529" si="15">A465+1</f>
         <v>132</v>
       </c>
       <c r="B466" t="s">
@@ -11748,6 +11751,113 @@
         <v>8</v>
       </c>
       <c r="C521">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3">
+      <c r="A522">
+        <v>172</v>
+      </c>
+      <c r="B522" t="s">
+        <v>8</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3">
+      <c r="A523">
+        <f t="shared" si="15"/>
+        <v>173</v>
+      </c>
+      <c r="B523" t="s">
+        <v>97</v>
+      </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3">
+      <c r="A524">
+        <f t="shared" si="15"/>
+        <v>174</v>
+      </c>
+      <c r="B524" t="s">
+        <v>11</v>
+      </c>
+      <c r="C524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3">
+      <c r="A525">
+        <f t="shared" si="15"/>
+        <v>175</v>
+      </c>
+      <c r="B525" t="s">
+        <v>10</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3">
+      <c r="A526">
+        <f t="shared" si="15"/>
+        <v>176</v>
+      </c>
+      <c r="B526" t="s">
+        <v>8</v>
+      </c>
+      <c r="C526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3">
+      <c r="A527">
+        <f t="shared" si="15"/>
+        <v>177</v>
+      </c>
+      <c r="B527" t="s">
+        <v>9</v>
+      </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528">
+        <f t="shared" si="15"/>
+        <v>178</v>
+      </c>
+      <c r="B528" t="s">
+        <v>11</v>
+      </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3">
+      <c r="A529">
+        <f t="shared" si="15"/>
+        <v>179</v>
+      </c>
+      <c r="B529" t="s">
+        <v>10</v>
+      </c>
+      <c r="C529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3">
+      <c r="A530">
+        <f t="shared" ref="A530" si="16">A529+1</f>
+        <v>180</v>
+      </c>
+      <c r="B530" t="s">
+        <v>10</v>
+      </c>
+      <c r="C530">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B871E3-53D0-46CF-BCA2-CC931A6184D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906CA461-213D-44B4-BAAA-043E1720E254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="98">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5553,7 +5553,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I530"/>
+  <dimension ref="A2:I535"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11851,13 +11851,73 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
-        <f t="shared" ref="A530" si="16">A529+1</f>
+        <f t="shared" ref="A530:A535" si="16">A529+1</f>
         <v>180</v>
       </c>
       <c r="B530" t="s">
         <v>10</v>
       </c>
       <c r="C530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3">
+      <c r="A531">
+        <f t="shared" si="16"/>
+        <v>181</v>
+      </c>
+      <c r="B531" t="s">
+        <v>9</v>
+      </c>
+      <c r="C531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3">
+      <c r="A532">
+        <f t="shared" si="16"/>
+        <v>182</v>
+      </c>
+      <c r="B532" t="s">
+        <v>11</v>
+      </c>
+      <c r="C532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3">
+      <c r="A533">
+        <f t="shared" si="16"/>
+        <v>183</v>
+      </c>
+      <c r="B533" t="s">
+        <v>8</v>
+      </c>
+      <c r="C533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3">
+      <c r="A534">
+        <f t="shared" si="16"/>
+        <v>184</v>
+      </c>
+      <c r="B534" t="s">
+        <v>8</v>
+      </c>
+      <c r="C534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3">
+      <c r="A535">
+        <f t="shared" si="16"/>
+        <v>185</v>
+      </c>
+      <c r="B535" t="s">
+        <v>9</v>
+      </c>
+      <c r="C535">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906CA461-213D-44B4-BAAA-043E1720E254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15465B-7AE5-4962-A4DA-58D5DB7900CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="98">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5553,7 +5553,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I535"/>
+  <dimension ref="A2:I540"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11851,7 +11851,7 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
-        <f t="shared" ref="A530:A535" si="16">A529+1</f>
+        <f t="shared" ref="A530:A540" si="16">A529+1</f>
         <v>180</v>
       </c>
       <c r="B530" t="s">
@@ -11918,6 +11918,66 @@
         <v>9</v>
       </c>
       <c r="C535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3">
+      <c r="A536">
+        <f t="shared" si="16"/>
+        <v>186</v>
+      </c>
+      <c r="B536" t="s">
+        <v>8</v>
+      </c>
+      <c r="C536">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3">
+      <c r="A537">
+        <f t="shared" si="16"/>
+        <v>187</v>
+      </c>
+      <c r="B537" t="s">
+        <v>11</v>
+      </c>
+      <c r="C537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3">
+      <c r="A538">
+        <f t="shared" si="16"/>
+        <v>188</v>
+      </c>
+      <c r="B538" t="s">
+        <v>8</v>
+      </c>
+      <c r="C538">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3">
+      <c r="A539">
+        <f t="shared" si="16"/>
+        <v>189</v>
+      </c>
+      <c r="B539" t="s">
+        <v>9</v>
+      </c>
+      <c r="C539">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3">
+      <c r="A540">
+        <f t="shared" si="16"/>
+        <v>190</v>
+      </c>
+      <c r="B540" t="s">
+        <v>10</v>
+      </c>
+      <c r="C540">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15465B-7AE5-4962-A4DA-58D5DB7900CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE13D0F-E7A0-48C5-8BE0-6CF8A33B4E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4125" yWindow="0" windowWidth="14655" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="102">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -477,6 +477,22 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -5553,7 +5569,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I540"/>
+  <dimension ref="A2:I550"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11851,7 +11867,7 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
-        <f t="shared" ref="A530:A540" si="16">A529+1</f>
+        <f t="shared" ref="A530:A551" si="16">A529+1</f>
         <v>180</v>
       </c>
       <c r="B530" t="s">
@@ -11978,6 +11994,125 @@
         <v>10</v>
       </c>
       <c r="C540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3">
+      <c r="A541">
+        <v>101</v>
+      </c>
+      <c r="B541" t="s">
+        <v>98</v>
+      </c>
+      <c r="C541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3">
+      <c r="A542">
+        <f t="shared" si="16"/>
+        <v>102</v>
+      </c>
+      <c r="B542" t="s">
+        <v>98</v>
+      </c>
+      <c r="C542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3">
+      <c r="A543">
+        <f t="shared" si="16"/>
+        <v>103</v>
+      </c>
+      <c r="B543" t="s">
+        <v>99</v>
+      </c>
+      <c r="C543">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3">
+      <c r="A544">
+        <f t="shared" si="16"/>
+        <v>104</v>
+      </c>
+      <c r="B544" t="s">
+        <v>99</v>
+      </c>
+      <c r="C544">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3">
+      <c r="A545">
+        <f t="shared" si="16"/>
+        <v>105</v>
+      </c>
+      <c r="B545" t="s">
+        <v>100</v>
+      </c>
+      <c r="C545">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3">
+      <c r="A546">
+        <f t="shared" si="16"/>
+        <v>106</v>
+      </c>
+      <c r="B546" t="s">
+        <v>98</v>
+      </c>
+      <c r="C546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3">
+      <c r="A547">
+        <f t="shared" si="16"/>
+        <v>107</v>
+      </c>
+      <c r="B547" t="s">
+        <v>99</v>
+      </c>
+      <c r="C547">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3">
+      <c r="A548">
+        <f t="shared" si="16"/>
+        <v>108</v>
+      </c>
+      <c r="B548" t="s">
+        <v>100</v>
+      </c>
+      <c r="C548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3">
+      <c r="A549">
+        <f t="shared" si="16"/>
+        <v>109</v>
+      </c>
+      <c r="B549" t="s">
+        <v>98</v>
+      </c>
+      <c r="C549">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3">
+      <c r="A550">
+        <f t="shared" si="16"/>
+        <v>110</v>
+      </c>
+      <c r="B550" t="s">
+        <v>101</v>
+      </c>
+      <c r="C550">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE13D0F-E7A0-48C5-8BE0-6CF8A33B4E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8B58B6-DBF8-4A3E-9764-22BCC896919F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="0" windowWidth="14655" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8190" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="106">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -492,6 +492,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5569,7 +5585,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I550"/>
+  <dimension ref="A2:I560"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11867,7 +11883,7 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
-        <f t="shared" ref="A530:A551" si="16">A529+1</f>
+        <f t="shared" ref="A530:A560" si="16">A529+1</f>
         <v>180</v>
       </c>
       <c r="B530" t="s">
@@ -12113,6 +12129,126 @@
         <v>101</v>
       </c>
       <c r="C550">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3">
+      <c r="A551">
+        <f t="shared" si="16"/>
+        <v>111</v>
+      </c>
+      <c r="B551" t="s">
+        <v>102</v>
+      </c>
+      <c r="C551">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3">
+      <c r="A552">
+        <f t="shared" si="16"/>
+        <v>112</v>
+      </c>
+      <c r="B552" t="s">
+        <v>103</v>
+      </c>
+      <c r="C552">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3">
+      <c r="A553">
+        <f t="shared" si="16"/>
+        <v>113</v>
+      </c>
+      <c r="B553" t="s">
+        <v>102</v>
+      </c>
+      <c r="C553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3">
+      <c r="A554">
+        <f t="shared" si="16"/>
+        <v>114</v>
+      </c>
+      <c r="B554" t="s">
+        <v>104</v>
+      </c>
+      <c r="C554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3">
+      <c r="A555">
+        <f t="shared" si="16"/>
+        <v>115</v>
+      </c>
+      <c r="B555" t="s">
+        <v>105</v>
+      </c>
+      <c r="C555">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3">
+      <c r="A556">
+        <f t="shared" si="16"/>
+        <v>116</v>
+      </c>
+      <c r="B556" t="s">
+        <v>105</v>
+      </c>
+      <c r="C556">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3">
+      <c r="A557">
+        <f t="shared" si="16"/>
+        <v>117</v>
+      </c>
+      <c r="B557" t="s">
+        <v>102</v>
+      </c>
+      <c r="C557">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3">
+      <c r="A558">
+        <f t="shared" si="16"/>
+        <v>118</v>
+      </c>
+      <c r="B558" t="s">
+        <v>105</v>
+      </c>
+      <c r="C558">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3">
+      <c r="A559">
+        <f t="shared" si="16"/>
+        <v>119</v>
+      </c>
+      <c r="B559" t="s">
+        <v>102</v>
+      </c>
+      <c r="C559">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3">
+      <c r="A560">
+        <f t="shared" si="16"/>
+        <v>120</v>
+      </c>
+      <c r="B560" t="s">
+        <v>105</v>
+      </c>
+      <c r="C560">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8B58B6-DBF8-4A3E-9764-22BCC896919F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17EB3D6-A2BA-48BF-8900-73B100F22A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8190" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4755" yWindow="945" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="112">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -508,6 +508,33 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>burdens</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>荷物</t>
+    <rPh sb="0" eb="2">
+      <t>ニモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>burden</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5585,7 +5612,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I560"/>
+  <dimension ref="A2:I570"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11883,7 +11910,7 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
-        <f t="shared" ref="A530:A560" si="16">A529+1</f>
+        <f t="shared" ref="A530:A570" si="16">A529+1</f>
         <v>180</v>
       </c>
       <c r="B530" t="s">
@@ -12060,7 +12087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:3">
+    <row r="545" spans="1:6">
       <c r="A545">
         <f t="shared" si="16"/>
         <v>105</v>
@@ -12072,7 +12099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:3">
+    <row r="546" spans="1:6">
       <c r="A546">
         <f t="shared" si="16"/>
         <v>106</v>
@@ -12084,7 +12111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:3">
+    <row r="547" spans="1:6">
       <c r="A547">
         <f t="shared" si="16"/>
         <v>107</v>
@@ -12096,7 +12123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:3">
+    <row r="548" spans="1:6">
       <c r="A548">
         <f t="shared" si="16"/>
         <v>108</v>
@@ -12108,7 +12135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:3">
+    <row r="549" spans="1:6">
       <c r="A549">
         <f t="shared" si="16"/>
         <v>109</v>
@@ -12120,7 +12147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:3">
+    <row r="550" spans="1:6">
       <c r="A550">
         <f t="shared" si="16"/>
         <v>110</v>
@@ -12132,7 +12159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:3">
+    <row r="551" spans="1:6">
       <c r="A551">
         <f t="shared" si="16"/>
         <v>111</v>
@@ -12144,7 +12171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:3">
+    <row r="552" spans="1:6">
       <c r="A552">
         <f t="shared" si="16"/>
         <v>112</v>
@@ -12156,7 +12183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:3">
+    <row r="553" spans="1:6">
       <c r="A553">
         <f t="shared" si="16"/>
         <v>113</v>
@@ -12168,7 +12195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:3">
+    <row r="554" spans="1:6">
       <c r="A554">
         <f t="shared" si="16"/>
         <v>114</v>
@@ -12180,7 +12207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:3">
+    <row r="555" spans="1:6">
       <c r="A555">
         <f t="shared" si="16"/>
         <v>115</v>
@@ -12192,7 +12219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:3">
+    <row r="556" spans="1:6">
       <c r="A556">
         <f t="shared" si="16"/>
         <v>116</v>
@@ -12204,7 +12231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:3">
+    <row r="557" spans="1:6">
       <c r="A557">
         <f t="shared" si="16"/>
         <v>117</v>
@@ -12216,7 +12243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:3">
+    <row r="558" spans="1:6">
       <c r="A558">
         <f t="shared" si="16"/>
         <v>118</v>
@@ -12227,8 +12254,14 @@
       <c r="C558">
         <v>1</v>
       </c>
-    </row>
-    <row r="559" spans="1:3">
+      <c r="E558" t="s">
+        <v>109</v>
+      </c>
+      <c r="F558" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6">
       <c r="A559">
         <f t="shared" si="16"/>
         <v>119</v>
@@ -12239,8 +12272,11 @@
       <c r="C559">
         <v>1</v>
       </c>
-    </row>
-    <row r="560" spans="1:3">
+      <c r="E559" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6">
       <c r="A560">
         <f t="shared" si="16"/>
         <v>120</v>
@@ -12250,6 +12286,129 @@
       </c>
       <c r="C560">
         <v>1</v>
+      </c>
+      <c r="E560" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3">
+      <c r="A561">
+        <f t="shared" si="16"/>
+        <v>121</v>
+      </c>
+      <c r="B561" t="s">
+        <v>106</v>
+      </c>
+      <c r="C561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3">
+      <c r="A562">
+        <f t="shared" si="16"/>
+        <v>122</v>
+      </c>
+      <c r="B562" t="s">
+        <v>107</v>
+      </c>
+      <c r="C562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3">
+      <c r="A563">
+        <f t="shared" si="16"/>
+        <v>123</v>
+      </c>
+      <c r="B563" t="s">
+        <v>107</v>
+      </c>
+      <c r="C563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3">
+      <c r="A564">
+        <f t="shared" si="16"/>
+        <v>124</v>
+      </c>
+      <c r="B564" t="s">
+        <v>108</v>
+      </c>
+      <c r="C564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3">
+      <c r="A565">
+        <f t="shared" si="16"/>
+        <v>125</v>
+      </c>
+      <c r="B565" t="s">
+        <v>106</v>
+      </c>
+      <c r="C565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3">
+      <c r="A566">
+        <f t="shared" si="16"/>
+        <v>126</v>
+      </c>
+      <c r="B566" t="s">
+        <v>108</v>
+      </c>
+      <c r="C566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3">
+      <c r="A567">
+        <f t="shared" si="16"/>
+        <v>127</v>
+      </c>
+      <c r="B567" t="s">
+        <v>108</v>
+      </c>
+      <c r="C567">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3">
+      <c r="A568">
+        <f t="shared" si="16"/>
+        <v>128</v>
+      </c>
+      <c r="B568" t="s">
+        <v>106</v>
+      </c>
+      <c r="C568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3">
+      <c r="A569">
+        <f t="shared" si="16"/>
+        <v>129</v>
+      </c>
+      <c r="B569" t="s">
+        <v>107</v>
+      </c>
+      <c r="C569">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3">
+      <c r="A570">
+        <f t="shared" si="16"/>
+        <v>130</v>
+      </c>
+      <c r="B570" t="s">
+        <v>108</v>
+      </c>
+      <c r="C570">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17EB3D6-A2BA-48BF-8900-73B100F22A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4418A7CA-5AFD-4608-AA9D-2F6CE107676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="945" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5175" yWindow="135" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="116">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -535,6 +535,22 @@
   </si>
   <si>
     <t>burden</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5612,7 +5628,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I570"/>
+  <dimension ref="A2:I579"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11910,7 +11926,7 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
-        <f t="shared" ref="A530:A570" si="16">A529+1</f>
+        <f t="shared" ref="A530:A579" si="16">A529+1</f>
         <v>180</v>
       </c>
       <c r="B530" t="s">
@@ -12409,6 +12425,108 @@
       </c>
       <c r="C570">
         <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3">
+      <c r="A571">
+        <f t="shared" si="16"/>
+        <v>131</v>
+      </c>
+      <c r="B571" t="s">
+        <v>112</v>
+      </c>
+      <c r="C571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3">
+      <c r="A572">
+        <f t="shared" si="16"/>
+        <v>132</v>
+      </c>
+      <c r="B572" t="s">
+        <v>112</v>
+      </c>
+      <c r="C572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3">
+      <c r="A573">
+        <f t="shared" si="16"/>
+        <v>133</v>
+      </c>
+      <c r="B573" t="s">
+        <v>113</v>
+      </c>
+      <c r="C573">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3">
+      <c r="A574">
+        <f t="shared" si="16"/>
+        <v>134</v>
+      </c>
+      <c r="B574" t="s">
+        <v>114</v>
+      </c>
+      <c r="C574">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3">
+      <c r="A575">
+        <f t="shared" si="16"/>
+        <v>135</v>
+      </c>
+      <c r="B575" t="s">
+        <v>114</v>
+      </c>
+      <c r="C575">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3">
+      <c r="A576">
+        <f t="shared" si="16"/>
+        <v>136</v>
+      </c>
+      <c r="B576" t="s">
+        <v>115</v>
+      </c>
+      <c r="C576">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3">
+      <c r="A577">
+        <f t="shared" si="16"/>
+        <v>137</v>
+      </c>
+      <c r="B577" t="s">
+        <v>113</v>
+      </c>
+      <c r="C577">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3">
+      <c r="A578">
+        <f t="shared" si="16"/>
+        <v>138</v>
+      </c>
+      <c r="B578" t="s">
+        <v>112</v>
+      </c>
+      <c r="C578">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3">
+      <c r="A579">
+        <f t="shared" si="16"/>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4418A7CA-5AFD-4608-AA9D-2F6CE107676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4E9EB7-2058-4A7A-BCF8-072A3CCB08FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5175" yWindow="135" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="119">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -539,6 +539,18 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5628,7 +5640,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I579"/>
+  <dimension ref="A2:I586"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -11926,7 +11938,7 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
-        <f t="shared" ref="A530:A579" si="16">A529+1</f>
+        <f t="shared" ref="A530:A585" si="16">A529+1</f>
         <v>180</v>
       </c>
       <c r="B530" t="s">
@@ -12527,6 +12539,96 @@
       <c r="A579">
         <f t="shared" si="16"/>
         <v>139</v>
+      </c>
+      <c r="B579" t="s">
+        <v>116</v>
+      </c>
+      <c r="C579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3">
+      <c r="A580">
+        <f t="shared" si="16"/>
+        <v>140</v>
+      </c>
+      <c r="B580" t="s">
+        <v>117</v>
+      </c>
+      <c r="C580">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3">
+      <c r="A581">
+        <f t="shared" si="16"/>
+        <v>141</v>
+      </c>
+      <c r="B581" t="s">
+        <v>117</v>
+      </c>
+      <c r="C581">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3">
+      <c r="A582">
+        <f t="shared" si="16"/>
+        <v>142</v>
+      </c>
+      <c r="B582" t="s">
+        <v>116</v>
+      </c>
+      <c r="C582">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3">
+      <c r="A583">
+        <f t="shared" si="16"/>
+        <v>143</v>
+      </c>
+      <c r="B583" t="s">
+        <v>118</v>
+      </c>
+      <c r="C583">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3">
+      <c r="A584">
+        <f t="shared" si="16"/>
+        <v>144</v>
+      </c>
+      <c r="B584" t="s">
+        <v>116</v>
+      </c>
+      <c r="C584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3">
+      <c r="A585">
+        <f t="shared" si="16"/>
+        <v>145</v>
+      </c>
+      <c r="B585" t="s">
+        <v>117</v>
+      </c>
+      <c r="C585">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3">
+      <c r="A586">
+        <f t="shared" ref="A586" si="17">A585+1</f>
+        <v>146</v>
+      </c>
+      <c r="B586" t="s">
+        <v>116</v>
+      </c>
+      <c r="C586">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4E9EB7-2058-4A7A-BCF8-072A3CCB08FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BE3F04-F775-4EB1-927F-C318F6B0C826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5175" yWindow="135" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="129">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -563,6 +563,49 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>exposition</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>展覧会</t>
+    <rPh sb="0" eb="3">
+      <t>テンランカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5640,7 +5683,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I586"/>
+  <dimension ref="A2:I603"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -12511,7 +12554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:3">
+    <row r="577" spans="1:7">
       <c r="A577">
         <f t="shared" si="16"/>
         <v>137</v>
@@ -12523,7 +12566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:3">
+    <row r="578" spans="1:7">
       <c r="A578">
         <f t="shared" si="16"/>
         <v>138</v>
@@ -12535,7 +12578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:3">
+    <row r="579" spans="1:7">
       <c r="A579">
         <f t="shared" si="16"/>
         <v>139</v>
@@ -12547,7 +12590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:3">
+    <row r="580" spans="1:7">
       <c r="A580">
         <f t="shared" si="16"/>
         <v>140</v>
@@ -12559,7 +12602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="581" spans="1:3">
+    <row r="581" spans="1:7">
       <c r="A581">
         <f t="shared" si="16"/>
         <v>141</v>
@@ -12571,7 +12614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="1:3">
+    <row r="582" spans="1:7">
       <c r="A582">
         <f t="shared" si="16"/>
         <v>142</v>
@@ -12583,7 +12626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:3">
+    <row r="583" spans="1:7">
       <c r="A583">
         <f t="shared" si="16"/>
         <v>143</v>
@@ -12595,7 +12638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:3">
+    <row r="584" spans="1:7">
       <c r="A584">
         <f t="shared" si="16"/>
         <v>144</v>
@@ -12607,7 +12650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:3">
+    <row r="585" spans="1:7">
       <c r="A585">
         <f t="shared" si="16"/>
         <v>145</v>
@@ -12619,15 +12662,225 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:3">
+    <row r="586" spans="1:7">
       <c r="A586">
-        <f t="shared" ref="A586" si="17">A585+1</f>
+        <f t="shared" ref="A586:A603" si="17">A585+1</f>
         <v>146</v>
       </c>
       <c r="B586" t="s">
         <v>116</v>
       </c>
       <c r="C586">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7">
+      <c r="A587">
+        <f t="shared" si="17"/>
+        <v>147</v>
+      </c>
+      <c r="B587" t="s">
+        <v>119</v>
+      </c>
+      <c r="C587">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7">
+      <c r="A588">
+        <f t="shared" si="17"/>
+        <v>148</v>
+      </c>
+      <c r="B588" t="s">
+        <v>120</v>
+      </c>
+      <c r="C588">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7">
+      <c r="A589">
+        <f t="shared" si="17"/>
+        <v>149</v>
+      </c>
+      <c r="B589" t="s">
+        <v>121</v>
+      </c>
+      <c r="C589">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7">
+      <c r="A590">
+        <f t="shared" si="17"/>
+        <v>150</v>
+      </c>
+      <c r="B590" t="s">
+        <v>119</v>
+      </c>
+      <c r="C590">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7">
+      <c r="A591">
+        <f t="shared" si="17"/>
+        <v>151</v>
+      </c>
+      <c r="B591" t="s">
+        <v>121</v>
+      </c>
+      <c r="C591">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7">
+      <c r="A592">
+        <f t="shared" si="17"/>
+        <v>152</v>
+      </c>
+      <c r="B592" t="s">
+        <v>122</v>
+      </c>
+      <c r="C592">
+        <v>1</v>
+      </c>
+      <c r="F592" t="s">
+        <v>125</v>
+      </c>
+      <c r="G592" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3">
+      <c r="A593">
+        <f t="shared" si="17"/>
+        <v>153</v>
+      </c>
+      <c r="B593" t="s">
+        <v>119</v>
+      </c>
+      <c r="C593">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3">
+      <c r="A594">
+        <f t="shared" si="17"/>
+        <v>154</v>
+      </c>
+      <c r="B594" t="s">
+        <v>121</v>
+      </c>
+      <c r="C594">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3">
+      <c r="A595">
+        <f t="shared" si="17"/>
+        <v>155</v>
+      </c>
+      <c r="B595" t="s">
+        <v>123</v>
+      </c>
+      <c r="C595">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3">
+      <c r="A596">
+        <f t="shared" si="17"/>
+        <v>156</v>
+      </c>
+      <c r="B596" t="s">
+        <v>124</v>
+      </c>
+      <c r="C596">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3">
+      <c r="A597">
+        <f t="shared" si="17"/>
+        <v>157</v>
+      </c>
+      <c r="B597" t="s">
+        <v>127</v>
+      </c>
+      <c r="C597">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3">
+      <c r="A598">
+        <f t="shared" si="17"/>
+        <v>158</v>
+      </c>
+      <c r="B598" t="s">
+        <v>128</v>
+      </c>
+      <c r="C598">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3">
+      <c r="A599">
+        <f t="shared" si="17"/>
+        <v>159</v>
+      </c>
+      <c r="B599" t="s">
+        <v>124</v>
+      </c>
+      <c r="C599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3">
+      <c r="A600">
+        <f t="shared" si="17"/>
+        <v>160</v>
+      </c>
+      <c r="B600" t="s">
+        <v>128</v>
+      </c>
+      <c r="C600">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3">
+      <c r="A601">
+        <f t="shared" si="17"/>
+        <v>161</v>
+      </c>
+      <c r="B601" t="s">
+        <v>124</v>
+      </c>
+      <c r="C601">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3">
+      <c r="A602">
+        <f t="shared" si="17"/>
+        <v>162</v>
+      </c>
+      <c r="B602" t="s">
+        <v>124</v>
+      </c>
+      <c r="C602">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3">
+      <c r="A603">
+        <f t="shared" si="17"/>
+        <v>163</v>
+      </c>
+      <c r="B603" t="s">
+        <v>127</v>
+      </c>
+      <c r="C603">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BE3F04-F775-4EB1-927F-C318F6B0C826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D4C247-61B6-4291-8059-C4E0B2EA6FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="133">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -598,6 +598,22 @@
     <rPh sb="0" eb="3">
       <t>テンランカイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5683,7 +5699,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I603"/>
+  <dimension ref="A2:I611"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -12664,7 +12680,7 @@
     </row>
     <row r="586" spans="1:7">
       <c r="A586">
-        <f t="shared" ref="A586:A603" si="17">A585+1</f>
+        <f t="shared" ref="A586:A611" si="17">A585+1</f>
         <v>146</v>
       </c>
       <c r="B586" t="s">
@@ -12881,6 +12897,102 @@
         <v>127</v>
       </c>
       <c r="C603">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3">
+      <c r="A604">
+        <f t="shared" si="17"/>
+        <v>164</v>
+      </c>
+      <c r="B604" t="s">
+        <v>129</v>
+      </c>
+      <c r="C604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3">
+      <c r="A605">
+        <f t="shared" si="17"/>
+        <v>165</v>
+      </c>
+      <c r="B605" t="s">
+        <v>129</v>
+      </c>
+      <c r="C605">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3">
+      <c r="A606">
+        <f t="shared" si="17"/>
+        <v>166</v>
+      </c>
+      <c r="B606" t="s">
+        <v>130</v>
+      </c>
+      <c r="C606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3">
+      <c r="A607">
+        <f t="shared" si="17"/>
+        <v>167</v>
+      </c>
+      <c r="B607" t="s">
+        <v>131</v>
+      </c>
+      <c r="C607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3">
+      <c r="A608">
+        <f t="shared" si="17"/>
+        <v>168</v>
+      </c>
+      <c r="B608" t="s">
+        <v>131</v>
+      </c>
+      <c r="C608">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3">
+      <c r="A609">
+        <f t="shared" si="17"/>
+        <v>169</v>
+      </c>
+      <c r="B609" t="s">
+        <v>132</v>
+      </c>
+      <c r="C609">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3">
+      <c r="A610">
+        <f t="shared" si="17"/>
+        <v>170</v>
+      </c>
+      <c r="B610" t="s">
+        <v>129</v>
+      </c>
+      <c r="C610">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3">
+      <c r="A611">
+        <f t="shared" si="17"/>
+        <v>171</v>
+      </c>
+      <c r="B611" t="s">
+        <v>129</v>
+      </c>
+      <c r="C611">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D4C247-61B6-4291-8059-C4E0B2EA6FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306B798E-5DD7-4058-A575-D31ED1A8D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6510" yWindow="1095" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="134">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -622,6 +622,10 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5699,7 +5703,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I611"/>
+  <dimension ref="A2:I615"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -12680,7 +12684,7 @@
     </row>
     <row r="586" spans="1:7">
       <c r="A586">
-        <f t="shared" ref="A586:A611" si="17">A585+1</f>
+        <f t="shared" ref="A586:A620" si="17">A585+1</f>
         <v>146</v>
       </c>
       <c r="B586" t="s">
@@ -12994,6 +12998,54 @@
       </c>
       <c r="C611">
         <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3">
+      <c r="A612">
+        <f t="shared" si="17"/>
+        <v>172</v>
+      </c>
+      <c r="B612" t="s">
+        <v>133</v>
+      </c>
+      <c r="C612">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3">
+      <c r="A613">
+        <f t="shared" si="17"/>
+        <v>173</v>
+      </c>
+      <c r="B613" t="s">
+        <v>133</v>
+      </c>
+      <c r="C613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3">
+      <c r="A614">
+        <f t="shared" si="17"/>
+        <v>174</v>
+      </c>
+      <c r="B614" t="s">
+        <v>133</v>
+      </c>
+      <c r="C614">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3">
+      <c r="A615">
+        <f t="shared" si="17"/>
+        <v>175</v>
+      </c>
+      <c r="B615" t="s">
+        <v>133</v>
+      </c>
+      <c r="C615">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306B798E-5DD7-4058-A575-D31ED1A8D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DFFA58-374D-44E9-891F-C9B947ABA371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6510" yWindow="1095" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="137">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -626,6 +626,18 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5703,7 +5715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I615"/>
+  <dimension ref="A2:I620"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -13046,6 +13058,66 @@
       </c>
       <c r="C615">
         <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3">
+      <c r="A616">
+        <f t="shared" si="17"/>
+        <v>176</v>
+      </c>
+      <c r="B616" t="s">
+        <v>134</v>
+      </c>
+      <c r="C616">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3">
+      <c r="A617">
+        <f t="shared" si="17"/>
+        <v>177</v>
+      </c>
+      <c r="B617" t="s">
+        <v>134</v>
+      </c>
+      <c r="C617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3">
+      <c r="A618">
+        <f t="shared" si="17"/>
+        <v>178</v>
+      </c>
+      <c r="B618" t="s">
+        <v>135</v>
+      </c>
+      <c r="C618">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3">
+      <c r="A619">
+        <f t="shared" si="17"/>
+        <v>179</v>
+      </c>
+      <c r="B619" t="s">
+        <v>134</v>
+      </c>
+      <c r="C619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3">
+      <c r="A620">
+        <f t="shared" si="17"/>
+        <v>180</v>
+      </c>
+      <c r="B620" t="s">
+        <v>136</v>
+      </c>
+      <c r="C620">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DFFA58-374D-44E9-891F-C9B947ABA371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10DF218-E0DB-4B28-9800-E79F80D49154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6510" yWindow="1095" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="140">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -638,6 +638,18 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5715,7 +5727,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I620"/>
+  <dimension ref="A2:I625"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -12696,7 +12708,7 @@
     </row>
     <row r="586" spans="1:7">
       <c r="A586">
-        <f t="shared" ref="A586:A620" si="17">A585+1</f>
+        <f t="shared" ref="A586:A625" si="17">A585+1</f>
         <v>146</v>
       </c>
       <c r="B586" t="s">
@@ -13118,6 +13130,66 @@
       </c>
       <c r="C620">
         <v>1</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3">
+      <c r="A621">
+        <f t="shared" si="17"/>
+        <v>181</v>
+      </c>
+      <c r="B621" t="s">
+        <v>137</v>
+      </c>
+      <c r="C621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3">
+      <c r="A622">
+        <f t="shared" si="17"/>
+        <v>182</v>
+      </c>
+      <c r="B622" t="s">
+        <v>138</v>
+      </c>
+      <c r="C622">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3">
+      <c r="A623">
+        <f t="shared" si="17"/>
+        <v>183</v>
+      </c>
+      <c r="B623" t="s">
+        <v>139</v>
+      </c>
+      <c r="C623">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3">
+      <c r="A624">
+        <f t="shared" si="17"/>
+        <v>184</v>
+      </c>
+      <c r="B624" t="s">
+        <v>139</v>
+      </c>
+      <c r="C624">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3">
+      <c r="A625">
+        <f t="shared" si="17"/>
+        <v>185</v>
+      </c>
+      <c r="B625" t="s">
+        <v>137</v>
+      </c>
+      <c r="C625">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10DF218-E0DB-4B28-9800-E79F80D49154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002FF8DE-B7A5-45C0-B833-9F952E49543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="1095" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="630" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="144">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -650,6 +650,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5727,7 +5743,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I625"/>
+  <dimension ref="A2:I630"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -12708,7 +12724,7 @@
     </row>
     <row r="586" spans="1:7">
       <c r="A586">
-        <f t="shared" ref="A586:A625" si="17">A585+1</f>
+        <f t="shared" ref="A586:A630" si="17">A585+1</f>
         <v>146</v>
       </c>
       <c r="B586" t="s">
@@ -13190,6 +13206,66 @@
       </c>
       <c r="C625">
         <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3">
+      <c r="A626">
+        <f t="shared" si="17"/>
+        <v>186</v>
+      </c>
+      <c r="B626" t="s">
+        <v>140</v>
+      </c>
+      <c r="C626">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3">
+      <c r="A627">
+        <f t="shared" si="17"/>
+        <v>187</v>
+      </c>
+      <c r="B627" t="s">
+        <v>141</v>
+      </c>
+      <c r="C627">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3">
+      <c r="A628">
+        <f t="shared" si="17"/>
+        <v>188</v>
+      </c>
+      <c r="B628" t="s">
+        <v>140</v>
+      </c>
+      <c r="C628">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3">
+      <c r="A629">
+        <f t="shared" si="17"/>
+        <v>189</v>
+      </c>
+      <c r="B629" t="s">
+        <v>142</v>
+      </c>
+      <c r="C629">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3">
+      <c r="A630">
+        <f t="shared" si="17"/>
+        <v>190</v>
+      </c>
+      <c r="B630" t="s">
+        <v>143</v>
+      </c>
+      <c r="C630">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002FF8DE-B7A5-45C0-B833-9F952E49543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E9D9D2-6257-4BE8-A023-1625C27D538E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="630" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="147">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -666,6 +666,18 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5743,7 +5755,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I630"/>
+  <dimension ref="A2:I635"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -12724,7 +12736,7 @@
     </row>
     <row r="586" spans="1:7">
       <c r="A586">
-        <f t="shared" ref="A586:A630" si="17">A585+1</f>
+        <f t="shared" ref="A586:A635" si="17">A585+1</f>
         <v>146</v>
       </c>
       <c r="B586" t="s">
@@ -13265,6 +13277,66 @@
         <v>143</v>
       </c>
       <c r="C630">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3">
+      <c r="A631">
+        <f t="shared" si="17"/>
+        <v>191</v>
+      </c>
+      <c r="B631" t="s">
+        <v>144</v>
+      </c>
+      <c r="C631">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3">
+      <c r="A632">
+        <f t="shared" si="17"/>
+        <v>192</v>
+      </c>
+      <c r="B632" t="s">
+        <v>144</v>
+      </c>
+      <c r="C632">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3">
+      <c r="A633">
+        <f t="shared" si="17"/>
+        <v>193</v>
+      </c>
+      <c r="B633" t="s">
+        <v>144</v>
+      </c>
+      <c r="C633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3">
+      <c r="A634">
+        <f t="shared" si="17"/>
+        <v>194</v>
+      </c>
+      <c r="B634" t="s">
+        <v>145</v>
+      </c>
+      <c r="C634">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3">
+      <c r="A635">
+        <f t="shared" si="17"/>
+        <v>195</v>
+      </c>
+      <c r="B635" t="s">
+        <v>146</v>
+      </c>
+      <c r="C635">
         <v>1</v>
       </c>
     </row>

--- a/l_r/3rd.xlsx
+++ b/l_r/3rd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E9D9D2-6257-4BE8-A023-1625C27D538E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4E8229-F7F5-4B29-9D60-0680254D0F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="630" windowWidth="21600" windowHeight="14385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="151">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -678,6 +678,22 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5755,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:I635"/>
+  <dimension ref="A2:I640"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:7">
@@ -12736,7 +12752,7 @@
     </row>
     <row r="586" spans="1:7">
       <c r="A586">
-        <f t="shared" ref="A586:A635" si="17">A585+1</f>
+        <f t="shared" ref="A586:A640" si="17">A585+1</f>
         <v>146</v>
       </c>
       <c r="B586" t="s">
@@ -13337,6 +13353,66 @@
         <v>146</v>
       </c>
       <c r="C635">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3">
+      <c r="A636">
+        <f t="shared" si="17"/>
+        <v>196</v>
+      </c>
+      <c r="B636" t="s">
+        <v>147</v>
+      </c>
+      <c r="C636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3">
+      <c r="A637">
+        <f t="shared" si="17"/>
+        <v>197</v>
+      </c>
+      <c r="B637" t="s">
+        <v>148</v>
+      </c>
+      <c r="C637">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3">
+      <c r="A638">
+        <f t="shared" si="17"/>
+        <v>198</v>
+      </c>
+      <c r="B638" t="s">
+        <v>149</v>
+      </c>
+      <c r="C638">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3">
+      <c r="A639">
+        <f t="shared" si="17"/>
+        <v>199</v>
+      </c>
+      <c r="B639" t="s">
+        <v>150</v>
+      </c>
+      <c r="C639">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3">
+      <c r="A640">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="B640" t="s">
+        <v>149</v>
+      </c>
+      <c r="C640">
         <v>1</v>
       </c>
     </row>
